--- a/jogos_2024-10-17.xlsx
+++ b/jogos_2024-10-17.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,25 +772,25 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>PSIS Semarang</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="L3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="M3" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="N3" t="n">
+        <v>10</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="P3" t="n">
         <v>2.75</v>
       </c>
-      <c r="M3" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="N3" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="O3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2.05</v>
-      </c>
       <c r="Q3" t="n">
-        <v>3.1</v>
+        <v>7</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -831,22 +831,22 @@
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="X3" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.13</v>
+        <v>1.42</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.63</v>
+        <v>2.65</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -856,14 +856,14 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
+          <t>['35']</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>['24', '88']</t>
-        </is>
-      </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
@@ -871,10 +871,10 @@
         <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>2.25</v>
+        <v>1.2</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.83</v>
+        <v>4.5</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45582.375</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,81 +901,81 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>PSIS Semarang</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
         <v>1</v>
       </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.22</v>
+        <v>2.75</v>
       </c>
       <c r="M4" t="n">
-        <v>6.25</v>
+        <v>3.05</v>
       </c>
       <c r="N4" t="n">
-        <v>10</v>
+        <v>2.45</v>
       </c>
       <c r="O4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="X4" t="n">
         <v>1.67</v>
       </c>
-      <c r="P4" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>7</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.75</v>
-      </c>
       <c r="Y4" t="n">
-        <v>1.42</v>
+        <v>2.13</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.65</v>
+        <v>1.63</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -985,12 +985,12 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>['35']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['24', '88']</t>
         </is>
       </c>
       <c r="AG4" t="n">
@@ -1000,10 +1000,10 @@
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.2</v>
+        <v>2.25</v>
       </c>
       <c r="AJ4" t="n">
-        <v>4.5</v>
+        <v>1.83</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45582.375</v>
@@ -1546,22 +1546,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Plateau United</t>
+          <t>Rivers United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Remo Stars</t>
+          <t>Shooting Stars</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1572,22 +1572,22 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.75</v>
+        <v>1.36</v>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="N9" t="n">
-        <v>4.75</v>
+        <v>8.5</v>
       </c>
       <c r="O9" t="n">
-        <v>2.38</v>
+        <v>1.95</v>
       </c>
       <c r="P9" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>6</v>
+        <v>9.5</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1605,16 +1605,16 @@
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="X9" t="n">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1630,12 +1630,12 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>['4', '64', '71']</t>
+          <t>['51', '65']</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>['83']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG9" t="n">
@@ -1645,10 +1645,10 @@
         <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AJ9" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45582.5</v>
@@ -1804,22 +1804,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Rivers United</t>
+          <t>Plateau United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Shooting Stars</t>
+          <t>Remo Stars</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1830,22 +1830,22 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.36</v>
+        <v>1.75</v>
       </c>
       <c r="M11" t="n">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="N11" t="n">
-        <v>8.5</v>
+        <v>4.75</v>
       </c>
       <c r="O11" t="n">
-        <v>1.95</v>
+        <v>2.38</v>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="Q11" t="n">
-        <v>9.5</v>
+        <v>6</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1863,50 +1863,50 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="X11" t="n">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="Z11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>['4', '64', '71']</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>['83']</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
         <v>1.5</v>
       </c>
-      <c r="AA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>['51', '65']</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AJ11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45582.5</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,22 +1933,22 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Heartland</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Ikorodu City</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1959,22 +1959,22 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.15</v>
+        <v>1.55</v>
       </c>
       <c r="M12" t="n">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="N12" t="n">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="O12" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="P12" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.33</v>
+        <v>7</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1992,22 +1992,22 @@
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="X12" t="n">
-        <v>2.4</v>
+        <v>2.21</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2017,12 +2017,12 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>['45', '45+7', '54']</t>
+          <t>['66']</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>['26', '89']</t>
+          <t>['5']</t>
         </is>
       </c>
       <c r="AG12" t="n">
@@ -2032,10 +2032,10 @@
         <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.75</v>
+        <v>4.5</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45582.5</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,22 +2062,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Heartland</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ikorodu City</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -2088,22 +2088,22 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.55</v>
+        <v>2.15</v>
       </c>
       <c r="M13" t="n">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="N13" t="n">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="O13" t="n">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="P13" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="Q13" t="n">
-        <v>7</v>
+        <v>4.33</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -2121,22 +2121,22 @@
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="X13" t="n">
-        <v>2.21</v>
+        <v>2.4</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2146,12 +2146,12 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>['66']</t>
+          <t>['45', '45+7', '54']</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>['5']</t>
+          <t>['26', '89']</t>
         </is>
       </c>
       <c r="AG13" t="n">
@@ -2161,10 +2161,10 @@
         <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="AJ13" t="n">
-        <v>4.5</v>
+        <v>2.75</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45582.5</v>
@@ -2320,19 +2320,19 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Aqaba</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -2346,34 +2346,34 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>7</v>
+        <v>3.9</v>
       </c>
       <c r="M15" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="N15" t="n">
-        <v>1.38</v>
+        <v>1.9</v>
       </c>
       <c r="O15" t="n">
-        <v>7</v>
+        <v>4.75</v>
       </c>
       <c r="P15" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.91</v>
+        <v>2.63</v>
       </c>
       <c r="R15" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="S15" t="n">
-        <v>3.25</v>
+        <v>2.63</v>
       </c>
       <c r="T15" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="U15" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -2385,31 +2385,31 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.85</v>
+        <v>2.38</v>
       </c>
       <c r="Z15" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AB15" t="n">
         <v>1.95</v>
       </c>
-      <c r="AA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>0</v>
-      </c>
       <c r="AC15" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['47']</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>['81', '82']</t>
+          <t>['64', '64', '81']</t>
         </is>
       </c>
       <c r="AG15" t="n">
@@ -2419,10 +2419,10 @@
         <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>4.33</v>
+        <v>2.88</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.29</v>
+        <v>1.62</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45582.57291666666</v>
@@ -2449,19 +2449,19 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aqaba</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -2475,70 +2475,70 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.9</v>
+        <v>7</v>
       </c>
       <c r="M16" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="N16" t="n">
-        <v>1.9</v>
+        <v>1.38</v>
       </c>
       <c r="O16" t="n">
-        <v>4.75</v>
+        <v>7</v>
       </c>
       <c r="P16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z16" t="n">
         <v>1.95</v>
       </c>
-      <c r="Q16" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AA16" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>['47']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>['64', '64', '81']</t>
+          <t>['81', '82']</t>
         </is>
       </c>
       <c r="AG16" t="n">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>2.88</v>
+        <v>4.33</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.62</v>
+        <v>1.29</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45582.57291666666</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,22 +3094,22 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H21" t="n">
         <v>2</v>
       </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
         <v>2</v>
@@ -3120,83 +3120,83 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="M21" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="N21" t="n">
         <v>5.75</v>
       </c>
       <c r="O21" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="P21" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>6</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="X21" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC21" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q21" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="R21" t="n">
+      <c r="AD21" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>['34', '68']</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>['13', '36']</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AI21" t="n">
         <v>1.44</v>
       </c>
-      <c r="S21" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X21" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>['5', '18', '55', '66', '78']</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>['30', '39']</t>
-        </is>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AJ21" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45582.83333333334</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,22 +3223,22 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H22" t="n">
         <v>2</v>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J22" t="n">
         <v>2</v>
@@ -3249,83 +3249,83 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="M22" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="N22" t="n">
         <v>5.75</v>
       </c>
       <c r="O22" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="P22" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="Q22" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S22" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="T22" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="U22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W22" t="n">
         <v>1.3</v>
       </c>
-      <c r="V22" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.47</v>
-      </c>
       <c r="X22" t="n">
-        <v>2.29</v>
+        <v>2.91</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.53</v>
+        <v>1.9</v>
       </c>
       <c r="AA22" t="n">
-        <v>4.33</v>
+        <v>3.42</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>['34', '68']</t>
+          <t>['5', '18', '55', '66', '78']</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>['13', '36']</t>
+          <t>['30', '39']</t>
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AJ22" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45582.83333333334</v>
